--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_Auto_OV_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_Auto_OV_Fiets.xlsx
@@ -405,10 +405,10 @@
         <v>2199</v>
       </c>
       <c r="C3">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="D3">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="E3">
         <v>2210</v>
@@ -476,7 +476,7 @@
         <v>2204</v>
       </c>
       <c r="D7">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="E7">
         <v>2208</v>
@@ -510,7 +510,7 @@
         <v>2197</v>
       </c>
       <c r="D9">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="E9">
         <v>2201</v>
@@ -524,13 +524,13 @@
         <v>2057</v>
       </c>
       <c r="C10">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="D10">
-        <v>2136</v>
+        <v>2143</v>
       </c>
       <c r="E10">
-        <v>2157</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>2045</v>
+        <v>2053</v>
       </c>
       <c r="C11">
-        <v>2093</v>
+        <v>2106</v>
       </c>
       <c r="D11">
-        <v>2141</v>
+        <v>2149</v>
       </c>
       <c r="E11">
-        <v>2162</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -558,13 +558,13 @@
         <v>1814</v>
       </c>
       <c r="C12">
-        <v>1922</v>
+        <v>1943</v>
       </c>
       <c r="D12">
-        <v>2039</v>
+        <v>2057</v>
       </c>
       <c r="E12">
-        <v>2097</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -575,13 +575,13 @@
         <v>2023</v>
       </c>
       <c r="C13">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="D13">
-        <v>2118</v>
+        <v>2127</v>
       </c>
       <c r="E13">
-        <v>2145</v>
+        <v>2147</v>
       </c>
     </row>
   </sheetData>
